--- a/docs/downloads/经营分_鲁西省区__滨东片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁西省区__滨东片区_2026-10-18.xlsx
@@ -885,7 +885,7 @@
         <v>90</v>
       </c>
       <c r="I4" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2374,14 +2374,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>105</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>东营市</t>
+          <t>滨州市</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>6601192953538938888</t>
+          <t>7161790307015591976</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7天优品Premium(东营职业学院府前大街店)</t>
+          <t>希岸酒店滨州渤海十路航空学院店</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7天优品Premium酒店(东营职业学院府前大街店)</t>
+          <t>希岸酒店(滨州渤海十路航空学院店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3170,14 +3170,14 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3199,7 +3199,7 @@
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3234,22 +3234,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>东营市</t>
+          <t>滨州市</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>6601184646862473223</t>
+          <t>7574587996440102947</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7天酒店（东营广饶孙武路店）</t>
+          <t>白玉兰商务酒店（滨州无棣埕口镇政府店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7天酒店(东营广饶孙武路店)</t>
+          <t>白玉兰商务酒店(滨州无棣埕口镇政府店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3258,14 +3258,14 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -3287,7 +3287,7 @@
         <v>30</v>
       </c>
       <c r="Q31" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="R31" t="n">
         <v>30</v>
@@ -3322,22 +3322,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>东营市</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>6850361664999589902</t>
+          <t>6601192953538938888</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>喆啡酒店（滨州沾化汽车站店）</t>
+          <t>7天优品Premium(东营职业学院府前大街店)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>喆啡酒店(滨州沾化汽车站店)</t>
+          <t>7天优品Premium酒店(东营职业学院府前大街店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3410,34 +3410,34 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>东营市</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>7161790307015591976</t>
+          <t>6601184646862473223</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>希岸酒店滨州渤海十路航空学院店</t>
+          <t>7天酒店（东营广饶孙武路店）</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>希岸酒店(滨州渤海十路航空学院店)</t>
+          <t>7天酒店(东营广饶孙武路店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>120</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3503,17 +3503,17 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>7574587996440102947</t>
+          <t>6850361664999589902</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（滨州无棣埕口镇政府店）</t>
+          <t>喆啡酒店（滨州沾化汽车站店）</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(滨州无棣埕口镇政府店)</t>
+          <t>喆啡酒店(滨州沾化汽车站店)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
